--- a/Project-5-AdventureWorks-Sales-Performance-Analysis/excel/02_deep_dive/02_bikes_model_and_colour.xlsx
+++ b/Project-5-AdventureWorks-Sales-Performance-Analysis/excel/02_deep_dive/02_bikes_model_and_colour.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="39">
   <si>
     <t xml:space="preserve">modelname</t>
   </si>
@@ -140,6 +140,9 @@
   <si>
     <t xml:space="preserve">Profit_Delta</t>
   </si>
+  <si>
+    <t xml:space="preserve">model_and_color</t>
+  </si>
 </sst>
 </file>
 
@@ -155,6 +158,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -176,6 +180,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -187,6 +192,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00A933"/>
+        <bgColor rgb="FF008000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFBF00"/>
         <bgColor rgb="FFFF9900"/>
       </patternFill>
@@ -195,12 +206,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00A933"/>
-        <bgColor rgb="FF008000"/>
       </patternFill>
     </fill>
   </fills>
@@ -433,90 +438,108 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="20" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="23" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="23" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="20" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="20" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="23" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="23" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="22" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="22" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="26" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="27" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="23" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="23" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="23" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="23" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="12" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="12" xfId="27" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -524,31 +547,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="27" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="23" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="23" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="17" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="17" xfId="27" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="27" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -556,19 +579,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="23" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="22" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="23" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="27" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="22" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="22" xfId="27" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -576,27 +599,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="27" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="27" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="27" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="27" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="25" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="25" xfId="26" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="26" xfId="24" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="26" xfId="26" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -612,43 +635,47 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="23" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="23" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="27" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="15" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="15" xfId="25" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="27" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="24" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="26" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="7" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="7" xfId="25" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -660,60 +687,20 @@
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Pivot Table Corner" xfId="20"/>
-    <cellStyle name="Pivot Table Value" xfId="21"/>
-    <cellStyle name="Pivot Table Field" xfId="22"/>
-    <cellStyle name="Pivot Table Category" xfId="23"/>
-    <cellStyle name="Pivot Table Title" xfId="24"/>
+    <cellStyle name="Green" xfId="20"/>
+    <cellStyle name="Orange" xfId="21"/>
+    <cellStyle name="Pivot Table Category" xfId="22"/>
+    <cellStyle name="Pivot Table Corner" xfId="23"/>
+    <cellStyle name="Pivot Table Field" xfId="24"/>
     <cellStyle name="Pivot Table Result" xfId="25"/>
-    <cellStyle name="Orange" xfId="26"/>
-    <cellStyle name="Yellow" xfId="27"/>
-    <cellStyle name="Green" xfId="28"/>
+    <cellStyle name="Pivot Table Title" xfId="26"/>
+    <cellStyle name="Pivot Table Value" xfId="27"/>
+    <cellStyle name="Yellow" xfId="28"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00A933"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFBF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFCCCC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCC0000"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -727,7 +714,6 @@
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <fill>
@@ -3136,4071 +3122,4071 @@
   <dimension ref="A1:I140"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="11.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="4.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="2" width="16.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="11.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="5.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="4.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="3" width="16.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="2" t="n">
         <v>118</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>18762</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>7016.98800000001</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="3" t="n">
         <v>11745.012</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="2" t="n">
         <v>116</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>18444</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>6898.05600000001</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="3" t="n">
         <v>11545.944</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>16200</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>6058.80000000001</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="3" t="n">
         <v>10141.2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="2" t="n">
         <v>167</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>20040</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="3" t="n">
         <v>7494.96000000002</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>12545.04</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="0" t="s">
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="2" t="n">
         <v>301</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>616778.558200002</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="3" t="n">
         <v>332848.809999999</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="3" t="n">
         <v>283929.748200001</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="2" t="n">
         <v>278</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>569649.299600001</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="3" t="n">
         <v>307415.179999999</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="3" t="n">
         <v>262234.119600001</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="2" t="n">
         <v>268</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>549158.317600001</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>296357.08</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="3" t="n">
         <v>252801.237600001</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="0" t="s">
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="2" t="n">
         <v>251</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>514323.648200001</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="3" t="n">
         <v>277558.31</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="3" t="n">
         <v>236765.338200001</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="0" t="s">
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F10" s="2" t="n">
         <v>246</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>504078.157200001</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <v>272029.26</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="3" t="n">
         <v>232048.897200001</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="0" t="s">
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="2" t="n">
         <v>227</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="3" t="n">
         <v>465145.291400001</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="3" t="n">
         <v>251018.87</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="3" t="n">
         <v>214126.421400001</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="0" t="s">
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="F12" s="2" t="n">
         <v>274</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="3" t="n">
         <v>567568.970400003</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="3" t="n">
         <v>306292.5166</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="3" t="n">
         <v>261276.4538</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="0" t="s">
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="F13" s="2" t="n">
         <v>258</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="3" t="n">
         <v>534426.256800002</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="3" t="n">
         <v>288406.8222</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I13" s="3" t="n">
         <v>246019.4346</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="0" t="s">
+      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="F14" s="2" t="n">
         <v>277</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G14" s="3" t="n">
         <v>573783.229200003</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="3" t="n">
         <v>309646.0843</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" s="3" t="n">
         <v>264137.1449</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="0" t="s">
+      <c r="C15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="F15" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G15" s="3" t="n">
         <v>466069.410000002</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H15" s="3" t="n">
         <v>251517.577499999</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I15" s="3" t="n">
         <v>214551.8325</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="0" t="s">
+      <c r="C16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="2" t="n">
         <v>244</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G16" s="3" t="n">
         <v>505426.382400002</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="3" t="n">
         <v>272756.839599999</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="3" t="n">
         <v>232669.5428</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="0" t="s">
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="2" t="n">
         <v>248</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G17" s="3" t="n">
         <v>513712.060800002</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H17" s="3" t="n">
         <v>277228.2632</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="I17" s="3" t="n">
         <v>236483.7976</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G18" s="3" t="n">
         <v>43860.93</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="3" t="n">
         <v>23927.3688</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" s="3" t="n">
         <v>19933.5612</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="F19" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G19" s="3" t="n">
         <v>36935.52</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="3" t="n">
         <v>20149.3632</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="I19" s="3" t="n">
         <v>16786.1568</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="F20" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G20" s="3" t="n">
         <v>36166.03</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="3" t="n">
         <v>19729.5848</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" s="3" t="n">
         <v>16436.4452</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F21" s="1" t="n">
+      <c r="F21" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G21" s="3" t="n">
         <v>39243.99</v>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="H21" s="3" t="n">
         <v>21408.6984</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="I21" s="3" t="n">
         <v>17835.2916</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E22" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F22" s="1" t="n">
+      <c r="F22" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G22" s="3" t="n">
         <v>68484.61</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H22" s="3" t="n">
         <v>37360.2776</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="I22" s="3" t="n">
         <v>31124.3324</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="E23" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F23" s="1" t="n">
+      <c r="F23" s="2" t="n">
         <v>78</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="G23" s="3" t="n">
         <v>60020.22</v>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="H23" s="3" t="n">
         <v>32742.7152</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="I23" s="3" t="n">
         <v>27277.5048</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="E24" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F24" s="1" t="n">
+      <c r="F24" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G24" s="3" t="n">
         <v>60789.71</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H24" s="3" t="n">
         <v>33162.4936</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" s="3" t="n">
         <v>27627.2164</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="E25" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F25" s="1" t="n">
+      <c r="F25" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G25" s="3" t="n">
         <v>64637.1599999999</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H25" s="3" t="n">
         <v>35261.3856</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="I25" s="3" t="n">
         <v>29375.7744</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="0" t="s">
+      <c r="C26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="E26" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F26" s="1" t="n">
+      <c r="F26" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G26" s="3" t="n">
         <v>12959.76</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="3" t="n">
         <v>7069.9128</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="I26" s="3" t="n">
         <v>5889.8472</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="0" t="s">
+      <c r="C27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F27" s="1" t="n">
+      <c r="F27" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G27" s="3" t="n">
         <v>12419.77</v>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="H27" s="3" t="n">
         <v>6775.3331</v>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="I27" s="3" t="n">
         <v>5644.4369</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="0" t="s">
+      <c r="C28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="E28" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F28" s="1" t="n">
+      <c r="F28" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G28" s="3" t="n">
         <v>11339.79</v>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H28" s="3" t="n">
         <v>6186.1737</v>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="I28" s="3" t="n">
         <v>5153.6163</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" s="0" t="s">
+      <c r="C29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="E29" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F29" s="1" t="n">
+      <c r="F29" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G29" s="3" t="n">
         <v>7019.87</v>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="H29" s="3" t="n">
         <v>3829.5361</v>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="I29" s="3" t="n">
         <v>3190.3339</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="0" t="s">
+      <c r="C30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="E30" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F30" s="1" t="n">
+      <c r="F30" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G30" s="3" t="n">
         <v>9719.82</v>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H30" s="3" t="n">
         <v>5302.4346</v>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="I30" s="3" t="n">
         <v>4417.3854</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="0" t="s">
+      <c r="C31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E31" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F31" s="1" t="n">
+      <c r="F31" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G31" s="3" t="n">
         <v>13499.75</v>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="H31" s="3" t="n">
         <v>7364.4925</v>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="I31" s="3" t="n">
         <v>6135.2575</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32" s="0" t="s">
+      <c r="C32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E32" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F32" s="1" t="n">
+      <c r="F32" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G32" s="3" t="n">
         <v>14579.73</v>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="H32" s="3" t="n">
         <v>7953.6519</v>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="I32" s="3" t="n">
         <v>6626.0781</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D33" s="0" t="s">
+      <c r="C33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E33" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F33" s="1" t="n">
+      <c r="F33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G33" s="3" t="n">
         <v>17279.68</v>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="H33" s="3" t="n">
         <v>9426.55040000001</v>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="I33" s="3" t="n">
         <v>7853.12959999999</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" s="0" t="s">
+      <c r="C34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="E34" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F34" s="1" t="n">
+      <c r="F34" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G34" s="3" t="n">
         <v>19979.63</v>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="H34" s="3" t="n">
         <v>10899.4489</v>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="I34" s="3" t="n">
         <v>9080.18109999999</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" s="0" t="s">
+      <c r="C35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="E35" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F35" s="1" t="n">
+      <c r="F35" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G35" s="3" t="n">
         <v>15119.72</v>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="H35" s="3" t="n">
         <v>8248.23160000001</v>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="I35" s="3" t="n">
         <v>6871.4884</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D36" s="0" t="s">
+      <c r="C36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E36" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F36" s="1" t="n">
+      <c r="F36" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G36" s="3" t="n">
         <v>12429.78</v>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="H36" s="3" t="n">
         <v>6780.7938</v>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="I36" s="3" t="n">
         <v>5648.9862</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37" s="0" t="s">
+      <c r="C37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="E37" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F37" s="1" t="n">
+      <c r="F37" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G37" s="3" t="n">
         <v>10169.82</v>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="H37" s="3" t="n">
         <v>5547.9222</v>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="I37" s="3" t="n">
         <v>4621.8978</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C38" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D38" s="0" t="s">
+      <c r="C38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="E38" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F38" s="1" t="n">
+      <c r="F38" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G38" s="3" t="n">
         <v>11864.79</v>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H38" s="3" t="n">
         <v>6472.5759</v>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="I38" s="3" t="n">
         <v>5392.2141</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="0" t="s">
+      <c r="C39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E39" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F39" s="1" t="n">
+      <c r="F39" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G39" s="3" t="n">
         <v>9604.83</v>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="H39" s="3" t="n">
         <v>5239.7043</v>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="I39" s="3" t="n">
         <v>4365.1257</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D40" s="0" t="s">
+      <c r="C40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E40" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F40" s="1" t="n">
+      <c r="F40" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G40" s="3" t="n">
         <v>8474.85</v>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="H40" s="3" t="n">
         <v>4623.2685</v>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="I40" s="3" t="n">
         <v>3851.5815</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" s="0" t="s">
+      <c r="C41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E41" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F41" s="1" t="n">
+      <c r="F41" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G41" s="3" t="n">
         <v>16949.7</v>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="H41" s="3" t="n">
         <v>9246.537</v>
       </c>
-      <c r="I41" s="2" t="n">
+      <c r="I41" s="3" t="n">
         <v>7703.163</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D42" s="0" t="s">
+      <c r="C42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E42" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F42" s="1" t="n">
+      <c r="F42" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G42" s="3" t="n">
         <v>14689.74</v>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H42" s="3" t="n">
         <v>8013.6654</v>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="I42" s="3" t="n">
         <v>6676.0746</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D43" s="0" t="s">
+      <c r="C43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="E43" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F43" s="1" t="n">
+      <c r="F43" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G43" s="3" t="n">
         <v>15819.72</v>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="H43" s="3" t="n">
         <v>8630.1012</v>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="I43" s="3" t="n">
         <v>7189.6188</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D44" s="0" t="s">
+      <c r="C44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E44" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F44" s="1" t="n">
+      <c r="F44" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G44" s="3" t="n">
         <v>11864.79</v>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="H44" s="3" t="n">
         <v>6472.5759</v>
       </c>
-      <c r="I44" s="2" t="n">
+      <c r="I44" s="3" t="n">
         <v>5392.2141</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C45" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D45" s="0" t="s">
+      <c r="C45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E45" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F45" s="1" t="n">
+      <c r="F45" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G45" s="3" t="n">
         <v>15254.73</v>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="H45" s="3" t="n">
         <v>8321.8833</v>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="I45" s="3" t="n">
         <v>6932.8467</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D46" s="0" t="s">
+      <c r="C46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E46" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F46" s="1" t="n">
+      <c r="F46" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G46" s="3" t="n">
         <v>314145</v>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="H46" s="3" t="n">
         <v>190178.4672</v>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="I46" s="3" t="n">
         <v>123966.5328</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C47" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D47" s="0" t="s">
+      <c r="C47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E47" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F47" s="1" t="n">
+      <c r="F47" s="2" t="n">
         <v>147</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G47" s="3" t="n">
         <v>320689.6875</v>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="H47" s="3" t="n">
         <v>194140.5186</v>
       </c>
-      <c r="I47" s="2" t="n">
+      <c r="I47" s="3" t="n">
         <v>126549.1689</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C48" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D48" s="0" t="s">
+      <c r="C48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="E48" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F48" s="1" t="n">
+      <c r="F48" s="2" t="n">
         <v>151</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G48" s="3" t="n">
         <v>329415.9375</v>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="H48" s="3" t="n">
         <v>199423.2538</v>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="I48" s="3" t="n">
         <v>129992.6837</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C49" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D49" s="0" t="s">
+      <c r="C49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E49" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F49" s="1" t="n">
+      <c r="F49" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G49" s="3" t="n">
         <v>283603.125</v>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="H49" s="3" t="n">
         <v>171688.894</v>
       </c>
-      <c r="I49" s="2" t="n">
+      <c r="I49" s="3" t="n">
         <v>111914.231</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D50" s="0" t="s">
+      <c r="C50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E50" s="1" t="n">
+      <c r="E50" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F50" s="1" t="n">
+      <c r="F50" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G50" s="3" t="n">
         <v>117804.375</v>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="H50" s="3" t="n">
         <v>71316.9252</v>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="I50" s="3" t="n">
         <v>46487.4498</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D51" s="0" t="s">
+      <c r="C51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E51" s="1" t="n">
+      <c r="E51" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F51" s="1" t="n">
+      <c r="F51" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G51" s="3" t="n">
         <v>128712.1875</v>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="H51" s="3" t="n">
         <v>77920.3442</v>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="I51" s="3" t="n">
         <v>50791.8433</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D52" s="0" t="s">
+      <c r="C52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="E52" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F52" s="1" t="n">
+      <c r="F52" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G52" s="3" t="n">
         <v>124349.0625</v>
       </c>
-      <c r="H52" s="2" t="n">
+      <c r="H52" s="3" t="n">
         <v>75278.9766</v>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="I52" s="3" t="n">
         <v>49070.0859</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C53" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D53" s="0" t="s">
+      <c r="C53" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="E53" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F53" s="1" t="n">
+      <c r="F53" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G53" s="3" t="n">
         <v>139620</v>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="H53" s="3" t="n">
         <v>84523.7632</v>
       </c>
-      <c r="I53" s="2" t="n">
+      <c r="I53" s="3" t="n">
         <v>55096.2368</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D54" s="0" t="s">
+      <c r="C54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="E54" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F54" s="1" t="n">
+      <c r="F54" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G54" s="3" t="n">
         <v>171034.5</v>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="H54" s="3" t="n">
         <v>106315.048</v>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="I54" s="3" t="n">
         <v>64719.4520000001</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C55" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D55" s="0" t="s">
+      <c r="C55" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="E55" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F55" s="1" t="n">
+      <c r="F55" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G55" s="3" t="n">
         <v>173477.85</v>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="H55" s="3" t="n">
         <v>107833.8344</v>
       </c>
-      <c r="I55" s="2" t="n">
+      <c r="I55" s="3" t="n">
         <v>65644.0156000001</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D56" s="0" t="s">
+      <c r="C56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="E56" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F56" s="1" t="n">
+      <c r="F56" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G56" s="3" t="n">
         <v>117280.8</v>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="H56" s="3" t="n">
         <v>72901.7471999999</v>
       </c>
-      <c r="I56" s="2" t="n">
+      <c r="I56" s="3" t="n">
         <v>44379.0528</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C57" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D57" s="0" t="s">
+      <c r="C57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E57" s="1" t="n">
+      <c r="E57" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F57" s="1" t="n">
+      <c r="F57" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G57" s="3" t="n">
         <v>292329.375</v>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="H57" s="3" t="n">
         <v>176971.6292</v>
       </c>
-      <c r="I57" s="2" t="n">
+      <c r="I57" s="3" t="n">
         <v>115357.7458</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C58" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D58" s="0" t="s">
+      <c r="C58" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="E58" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F58" s="1" t="n">
+      <c r="F58" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G58" s="3" t="n">
         <v>137438.4375</v>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="H58" s="3" t="n">
         <v>83203.0794</v>
       </c>
-      <c r="I58" s="2" t="n">
+      <c r="I58" s="3" t="n">
         <v>54235.3581</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C59" s="0" t="s">
+      <c r="C59" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="D59" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="E59" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F59" s="1" t="n">
+      <c r="F59" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G59" s="3" t="n">
         <v>146285.14</v>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="H59" s="3" t="n">
         <v>93095.8599999999</v>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="I59" s="3" t="n">
         <v>53189.2800000001</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C60" s="0" t="s">
+      <c r="C60" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D60" s="0" t="s">
+      <c r="D60" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E60" s="1" t="n">
+      <c r="E60" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F60" s="1" t="n">
+      <c r="F60" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G60" s="3" t="n">
         <v>127574.25</v>
       </c>
-      <c r="H60" s="2" t="n">
+      <c r="H60" s="3" t="n">
         <v>81188.25</v>
       </c>
-      <c r="I60" s="2" t="n">
+      <c r="I60" s="3" t="n">
         <v>46386.0000000001</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C61" s="0" t="s">
+      <c r="C61" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D61" s="0" t="s">
+      <c r="D61" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E61" s="1" t="n">
+      <c r="E61" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F61" s="1" t="n">
+      <c r="F61" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G61" s="3" t="n">
         <v>117368.31</v>
       </c>
-      <c r="H61" s="2" t="n">
+      <c r="H61" s="3" t="n">
         <v>74693.19</v>
       </c>
-      <c r="I61" s="2" t="n">
+      <c r="I61" s="3" t="n">
         <v>42675.12</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C62" s="0" t="s">
+      <c r="C62" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="0" t="s">
+      <c r="D62" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E62" s="1" t="n">
+      <c r="E62" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F62" s="1" t="n">
+      <c r="F62" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G62" s="3" t="n">
         <v>137780.19</v>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="H62" s="3" t="n">
         <v>87683.3099999999</v>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="I62" s="3" t="n">
         <v>50096.8800000001</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C63" s="0" t="s">
+      <c r="C63" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D63" s="0" t="s">
+      <c r="D63" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E63" s="1" t="n">
+      <c r="E63" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="F63" s="2" t="n">
         <v>154</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G63" s="3" t="n">
         <v>261952.459999999</v>
       </c>
-      <c r="H63" s="2" t="n">
+      <c r="H63" s="3" t="n">
         <v>166706.54</v>
       </c>
-      <c r="I63" s="2" t="n">
+      <c r="I63" s="3" t="n">
         <v>95245.92</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C64" s="0" t="s">
+      <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D64" s="0" t="s">
+      <c r="D64" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="E64" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F64" s="1" t="n">
+      <c r="F64" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G64" s="3" t="n">
         <v>255148.5</v>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="H64" s="3" t="n">
         <v>162376.5</v>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="I64" s="3" t="n">
         <v>92772</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C65" s="0" t="s">
+      <c r="C65" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="0" t="s">
+      <c r="D65" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E65" s="1" t="n">
+      <c r="E65" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F65" s="1" t="n">
+      <c r="F65" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G65" s="3" t="n">
         <v>244942.56</v>
       </c>
-      <c r="H65" s="2" t="n">
+      <c r="H65" s="3" t="n">
         <v>155881.44</v>
       </c>
-      <c r="I65" s="2" t="n">
+      <c r="I65" s="3" t="n">
         <v>89061.12</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C66" s="0" t="s">
+      <c r="C66" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D66" s="0" t="s">
+      <c r="D66" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E66" s="1" t="n">
+      <c r="E66" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F66" s="1" t="n">
+      <c r="F66" s="2" t="n">
         <v>152</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G66" s="3" t="n">
         <v>258550.48</v>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="H66" s="3" t="n">
         <v>164541.52</v>
       </c>
-      <c r="I66" s="2" t="n">
+      <c r="I66" s="3" t="n">
         <v>94008.96</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C67" s="0" t="s">
+      <c r="C67" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D67" s="0" t="s">
+      <c r="D67" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="E67" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F67" s="1" t="n">
+      <c r="F67" s="2" t="n">
         <v>126</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G67" s="3" t="n">
         <v>126055.125</v>
       </c>
-      <c r="H67" s="2" t="n">
+      <c r="H67" s="3" t="n">
         <v>76311.7992</v>
       </c>
-      <c r="I67" s="2" t="n">
+      <c r="I67" s="3" t="n">
         <v>49743.3258</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C68" s="0" t="s">
+      <c r="C68" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D68" s="0" t="s">
+      <c r="D68" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="E68" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F68" s="1" t="n">
+      <c r="F68" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G68" s="3" t="n">
         <v>109047.6875</v>
       </c>
-      <c r="H68" s="2" t="n">
+      <c r="H68" s="3" t="n">
         <v>66015.7628</v>
       </c>
-      <c r="I68" s="2" t="n">
+      <c r="I68" s="3" t="n">
         <v>43031.9247</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C69" s="0" t="s">
+      <c r="C69" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D69" s="0" t="s">
+      <c r="D69" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E69" s="1" t="n">
+      <c r="E69" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F69" s="1" t="n">
+      <c r="F69" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G69" s="3" t="n">
         <v>128056</v>
       </c>
-      <c r="H69" s="2" t="n">
+      <c r="H69" s="3" t="n">
         <v>77523.0976</v>
       </c>
-      <c r="I69" s="2" t="n">
+      <c r="I69" s="3" t="n">
         <v>50532.9024</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C70" s="0" t="s">
+      <c r="C70" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D70" s="0" t="s">
+      <c r="D70" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E70" s="1" t="n">
+      <c r="E70" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F70" s="1" t="n">
+      <c r="F70" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G70" s="3" t="n">
         <v>138060.375</v>
       </c>
-      <c r="H70" s="2" t="n">
+      <c r="H70" s="3" t="n">
         <v>83579.5896</v>
       </c>
-      <c r="I70" s="2" t="n">
+      <c r="I70" s="3" t="n">
         <v>54480.7854</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C71" s="0" t="s">
+      <c r="C71" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="D71" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E71" s="1" t="n">
+      <c r="E71" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F71" s="1" t="n">
+      <c r="F71" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G71" s="3" t="n">
         <v>112049</v>
       </c>
-      <c r="H71" s="2" t="n">
+      <c r="H71" s="3" t="n">
         <v>67832.7104</v>
       </c>
-      <c r="I71" s="2" t="n">
+      <c r="I71" s="3" t="n">
         <v>44216.2896</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C72" s="0" t="s">
+      <c r="C72" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D72" s="0" t="s">
+      <c r="D72" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="E72" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F72" s="1" t="n">
+      <c r="F72" s="2" t="n">
         <v>123</v>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G72" s="3" t="n">
         <v>123053.8125</v>
       </c>
-      <c r="H72" s="2" t="n">
+      <c r="H72" s="3" t="n">
         <v>74494.8516</v>
       </c>
-      <c r="I72" s="2" t="n">
+      <c r="I72" s="3" t="n">
         <v>48558.9609</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C73" s="0" t="s">
+      <c r="C73" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D73" s="0" t="s">
+      <c r="D73" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="E73" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F73" s="1" t="n">
+      <c r="F73" s="2" t="n">
         <v>114</v>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="G73" s="3" t="n">
         <v>114049.875</v>
       </c>
-      <c r="H73" s="2" t="n">
+      <c r="H73" s="3" t="n">
         <v>69044.0088</v>
       </c>
-      <c r="I73" s="2" t="n">
+      <c r="I73" s="3" t="n">
         <v>45005.8662</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C74" s="0" t="s">
+      <c r="C74" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D74" s="0" t="s">
+      <c r="D74" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E74" s="1" t="n">
+      <c r="E74" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F74" s="1" t="n">
+      <c r="F74" s="2" t="n">
         <v>117</v>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="G74" s="3" t="n">
         <v>117051.1875</v>
       </c>
-      <c r="H74" s="2" t="n">
+      <c r="H74" s="3" t="n">
         <v>70860.9564</v>
       </c>
-      <c r="I74" s="2" t="n">
+      <c r="I74" s="3" t="n">
         <v>46190.2311</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C75" s="0" t="s">
+      <c r="C75" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D75" s="0" t="s">
+      <c r="D75" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E75" s="1" t="n">
+      <c r="E75" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F75" s="1" t="n">
+      <c r="F75" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="G75" s="3" t="n">
         <v>135059.0625</v>
       </c>
-      <c r="H75" s="2" t="n">
+      <c r="H75" s="3" t="n">
         <v>81762.642</v>
       </c>
-      <c r="I75" s="2" t="n">
+      <c r="I75" s="3" t="n">
         <v>53296.4205</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C76" s="0" t="s">
+      <c r="C76" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D76" s="0" t="s">
+      <c r="D76" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E76" s="1" t="n">
+      <c r="E76" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F76" s="1" t="n">
+      <c r="F76" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="G76" s="3" t="n">
         <v>112049</v>
       </c>
-      <c r="H76" s="2" t="n">
+      <c r="H76" s="3" t="n">
         <v>67832.7104</v>
       </c>
-      <c r="I76" s="2" t="n">
+      <c r="I76" s="3" t="n">
         <v>44216.2896</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C77" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D77" s="0" t="s">
+      <c r="C77" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E77" s="1" t="n">
+      <c r="E77" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F77" s="1" t="n">
+      <c r="F77" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="G77" s="3" t="n">
         <v>22371.1424</v>
       </c>
-      <c r="H77" s="2" t="n">
+      <c r="H77" s="3" t="n">
         <v>13220.6816</v>
       </c>
-      <c r="I77" s="2" t="n">
+      <c r="I77" s="3" t="n">
         <v>9150.4608</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="B78" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C78" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D78" s="0" t="s">
+      <c r="C78" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E78" s="1" t="n">
+      <c r="E78" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F78" s="1" t="n">
+      <c r="F78" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="G78" s="3" t="n">
         <v>20273.8478</v>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="H78" s="3" t="n">
         <v>11981.2427</v>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="I78" s="3" t="n">
         <v>8292.6051</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C79" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D79" s="0" t="s">
+      <c r="C79" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E79" s="1" t="n">
+      <c r="E79" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F79" s="1" t="n">
+      <c r="F79" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="G79" s="3" t="n">
         <v>13981.964</v>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="H79" s="3" t="n">
         <v>8262.926</v>
       </c>
-      <c r="I79" s="2" t="n">
+      <c r="I79" s="3" t="n">
         <v>5719.038</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C80" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D80" s="0" t="s">
+      <c r="C80" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E80" s="1" t="n">
+      <c r="E80" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F80" s="1" t="n">
+      <c r="F80" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="G80" s="3" t="n">
         <v>15380.1604</v>
       </c>
-      <c r="H80" s="2" t="n">
+      <c r="H80" s="3" t="n">
         <v>9089.2186</v>
       </c>
-      <c r="I80" s="2" t="n">
+      <c r="I80" s="3" t="n">
         <v>6290.9418</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C81" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D81" s="0" t="s">
+      <c r="C81" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E81" s="1" t="n">
+      <c r="E81" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F81" s="1" t="n">
+      <c r="F81" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="G81" s="3" t="n">
         <v>18875.6514</v>
       </c>
-      <c r="H81" s="2" t="n">
+      <c r="H81" s="3" t="n">
         <v>11154.9501</v>
       </c>
-      <c r="I81" s="2" t="n">
+      <c r="I81" s="3" t="n">
         <v>7720.7013</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="B82" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C82" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D82" s="0" t="s">
+      <c r="C82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E82" s="1" t="n">
+      <c r="E82" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F82" s="1" t="n">
+      <c r="F82" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="G82" s="3" t="n">
         <v>23070.2406</v>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="H82" s="3" t="n">
         <v>13633.8279</v>
       </c>
-      <c r="I82" s="2" t="n">
+      <c r="I82" s="3" t="n">
         <v>9436.4127</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C83" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D83" s="0" t="s">
+      <c r="C83" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E83" s="1" t="n">
+      <c r="E83" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F83" s="1" t="n">
+      <c r="F83" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="G83" s="3" t="n">
         <v>21672.0442</v>
       </c>
-      <c r="H83" s="2" t="n">
+      <c r="H83" s="3" t="n">
         <v>12807.5353</v>
       </c>
-      <c r="I83" s="2" t="n">
+      <c r="I83" s="3" t="n">
         <v>8864.5089</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C84" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D84" s="0" t="s">
+      <c r="C84" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E84" s="1" t="n">
+      <c r="E84" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F84" s="1" t="n">
+      <c r="F84" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="G84" s="2" t="n">
+      <c r="G84" s="3" t="n">
         <v>22371.1424</v>
       </c>
-      <c r="H84" s="2" t="n">
+      <c r="H84" s="3" t="n">
         <v>13220.6816</v>
       </c>
-      <c r="I84" s="2" t="n">
+      <c r="I84" s="3" t="n">
         <v>9150.4608</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C85" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D85" s="0" t="s">
+      <c r="C85" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E85" s="1" t="n">
+      <c r="E85" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F85" s="1" t="n">
+      <c r="F85" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="G85" s="2" t="n">
+      <c r="G85" s="3" t="n">
         <v>18875.6514</v>
       </c>
-      <c r="H85" s="2" t="n">
+      <c r="H85" s="3" t="n">
         <v>11154.9501</v>
       </c>
-      <c r="I85" s="2" t="n">
+      <c r="I85" s="3" t="n">
         <v>7720.7013</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="B86" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C86" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D86" s="0" t="s">
+      <c r="C86" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E86" s="1" t="n">
+      <c r="E86" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F86" s="1" t="n">
+      <c r="F86" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G86" s="2" t="n">
+      <c r="G86" s="3" t="n">
         <v>24468.437</v>
       </c>
-      <c r="H86" s="2" t="n">
+      <c r="H86" s="3" t="n">
         <v>14460.1205</v>
       </c>
-      <c r="I86" s="2" t="n">
+      <c r="I86" s="3" t="n">
         <v>10008.3165</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="B87" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C87" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D87" s="0" t="s">
+      <c r="C87" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E87" s="1" t="n">
+      <c r="E87" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F87" s="1" t="n">
+      <c r="F87" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="G87" s="3" t="n">
         <v>20972.946</v>
       </c>
-      <c r="H87" s="2" t="n">
+      <c r="H87" s="3" t="n">
         <v>12394.389</v>
       </c>
-      <c r="I87" s="2" t="n">
+      <c r="I87" s="3" t="n">
         <v>8578.557</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C88" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D88" s="0" t="s">
+      <c r="C88" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E88" s="1" t="n">
+      <c r="E88" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F88" s="1" t="n">
+      <c r="F88" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="G88" s="2" t="n">
+      <c r="G88" s="3" t="n">
         <v>10486.473</v>
       </c>
-      <c r="H88" s="2" t="n">
+      <c r="H88" s="3" t="n">
         <v>6197.1945</v>
       </c>
-      <c r="I88" s="2" t="n">
+      <c r="I88" s="3" t="n">
         <v>4289.2785</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="B89" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C89" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D89" s="0" t="s">
+      <c r="C89" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E89" s="1" t="n">
+      <c r="E89" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F89" s="1" t="n">
+      <c r="F89" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="G89" s="2" t="n">
+      <c r="G89" s="3" t="n">
         <v>80998.5000000001</v>
       </c>
-      <c r="H89" s="2" t="n">
+      <c r="H89" s="3" t="n">
         <v>51547.4399999999</v>
       </c>
-      <c r="I89" s="2" t="n">
+      <c r="I89" s="3" t="n">
         <v>29451.06</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B90" s="0" t="s">
+      <c r="B90" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C90" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D90" s="0" t="s">
+      <c r="C90" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E90" s="1" t="n">
+      <c r="E90" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F90" s="1" t="n">
+      <c r="F90" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="G90" s="2" t="n">
+      <c r="G90" s="3" t="n">
         <v>75598.6</v>
       </c>
-      <c r="H90" s="2" t="n">
+      <c r="H90" s="3" t="n">
         <v>48110.9439999999</v>
       </c>
-      <c r="I90" s="2" t="n">
+      <c r="I90" s="3" t="n">
         <v>27487.656</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="B91" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C91" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D91" s="0" t="s">
+      <c r="C91" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E91" s="1" t="n">
+      <c r="E91" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F91" s="1" t="n">
+      <c r="F91" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="G91" s="2" t="n">
+      <c r="G91" s="3" t="n">
         <v>84238.4400000001</v>
       </c>
-      <c r="H91" s="2" t="n">
+      <c r="H91" s="3" t="n">
         <v>53609.3375999999</v>
       </c>
-      <c r="I91" s="2" t="n">
+      <c r="I91" s="3" t="n">
         <v>30629.1024</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B92" s="0" t="s">
+      <c r="B92" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C92" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D92" s="0" t="s">
+      <c r="C92" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E92" s="1" t="n">
+      <c r="E92" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F92" s="1" t="n">
+      <c r="F92" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="G92" s="2" t="n">
+      <c r="G92" s="3" t="n">
         <v>80998.5000000001</v>
       </c>
-      <c r="H92" s="2" t="n">
+      <c r="H92" s="3" t="n">
         <v>51547.4399999999</v>
       </c>
-      <c r="I92" s="2" t="n">
+      <c r="I92" s="3" t="n">
         <v>29451.06</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="B93" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C93" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D93" s="0" t="s">
+      <c r="C93" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E93" s="1" t="n">
+      <c r="E93" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F93" s="1" t="n">
+      <c r="F93" s="2" t="n">
         <v>233</v>
       </c>
-      <c r="G93" s="2" t="n">
+      <c r="G93" s="3" t="n">
         <v>125817.670000001</v>
       </c>
-      <c r="H93" s="2" t="n">
+      <c r="H93" s="3" t="n">
         <v>80070.3567999999</v>
       </c>
-      <c r="I93" s="2" t="n">
+      <c r="I93" s="3" t="n">
         <v>45747.3132000001</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="B94" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C94" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D94" s="0" t="s">
+      <c r="C94" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E94" s="1" t="n">
+      <c r="E94" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F94" s="1" t="n">
+      <c r="F94" s="2" t="n">
         <v>199</v>
       </c>
-      <c r="G94" s="2" t="n">
+      <c r="G94" s="3" t="n">
         <v>107458.01</v>
       </c>
-      <c r="H94" s="2" t="n">
+      <c r="H94" s="3" t="n">
         <v>68386.2703999998</v>
       </c>
-      <c r="I94" s="2" t="n">
+      <c r="I94" s="3" t="n">
         <v>39071.7396000001</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="B95" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C95" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D95" s="0" t="s">
+      <c r="C95" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E95" s="1" t="n">
+      <c r="E95" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F95" s="1" t="n">
+      <c r="F95" s="2" t="n">
         <v>206</v>
       </c>
-      <c r="G95" s="2" t="n">
+      <c r="G95" s="3" t="n">
         <v>111237.94</v>
       </c>
-      <c r="H95" s="2" t="n">
+      <c r="H95" s="3" t="n">
         <v>70791.8175999998</v>
       </c>
-      <c r="I95" s="2" t="n">
+      <c r="I95" s="3" t="n">
         <v>40446.1224000001</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="B96" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C96" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D96" s="0" t="s">
+      <c r="C96" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E96" s="1" t="n">
+      <c r="E96" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F96" s="1" t="n">
+      <c r="F96" s="2" t="n">
         <v>188</v>
       </c>
-      <c r="G96" s="2" t="n">
+      <c r="G96" s="3" t="n">
         <v>101518.12</v>
       </c>
-      <c r="H96" s="2" t="n">
+      <c r="H96" s="3" t="n">
         <v>64606.1247999998</v>
       </c>
-      <c r="I96" s="2" t="n">
+      <c r="I96" s="3" t="n">
         <v>36911.9952000001</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B97" s="0" t="s">
+      <c r="B97" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C97" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D97" s="0" t="s">
+      <c r="C97" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E97" s="1" t="n">
+      <c r="E97" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F97" s="1" t="n">
+      <c r="F97" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="G97" s="2" t="n">
+      <c r="G97" s="3" t="n">
         <v>126355.71</v>
       </c>
-      <c r="H97" s="2" t="n">
+      <c r="H97" s="3" t="n">
         <v>78542.7087</v>
       </c>
-      <c r="I97" s="2" t="n">
+      <c r="I97" s="3" t="n">
         <v>47813.0013</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+      <c r="A98" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B98" s="0" t="s">
+      <c r="B98" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C98" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D98" s="0" t="s">
+      <c r="C98" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E98" s="1" t="n">
+      <c r="E98" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F98" s="1" t="n">
+      <c r="F98" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="G98" s="2" t="n">
+      <c r="G98" s="3" t="n">
         <v>126355.71</v>
       </c>
-      <c r="H98" s="2" t="n">
+      <c r="H98" s="3" t="n">
         <v>78542.7087</v>
       </c>
-      <c r="I98" s="2" t="n">
+      <c r="I98" s="3" t="n">
         <v>47813.0013</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+      <c r="A99" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="B99" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C99" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D99" s="0" t="s">
+      <c r="C99" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E99" s="1" t="n">
+      <c r="E99" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F99" s="1" t="n">
+      <c r="F99" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="G99" s="2" t="n">
+      <c r="G99" s="3" t="n">
         <v>143044.2</v>
       </c>
-      <c r="H99" s="2" t="n">
+      <c r="H99" s="3" t="n">
         <v>88916.274</v>
       </c>
-      <c r="I99" s="2" t="n">
+      <c r="I99" s="3" t="n">
         <v>54127.9260000001</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="B100" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C100" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D100" s="0" t="s">
+      <c r="C100" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E100" s="1" t="n">
+      <c r="E100" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F100" s="1" t="n">
+      <c r="F100" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="G100" s="2" t="n">
+      <c r="G100" s="3" t="n">
         <v>138276.06</v>
       </c>
-      <c r="H100" s="2" t="n">
+      <c r="H100" s="3" t="n">
         <v>85952.3982</v>
       </c>
-      <c r="I100" s="2" t="n">
+      <c r="I100" s="3" t="n">
         <v>52323.6618</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C101" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D101" s="0" t="s">
+      <c r="C101" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E101" s="1" t="n">
+      <c r="E101" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F101" s="1" t="n">
+      <c r="F101" s="2" t="n">
         <v>118</v>
       </c>
-      <c r="G101" s="2" t="n">
+      <c r="G101" s="3" t="n">
         <v>281320.260000001</v>
       </c>
-      <c r="H101" s="2" t="n">
+      <c r="H101" s="3" t="n">
         <v>174868.6722</v>
       </c>
-      <c r="I101" s="2" t="n">
+      <c r="I101" s="3" t="n">
         <v>106451.5878</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="B102" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C102" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D102" s="0" t="s">
+      <c r="C102" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E102" s="1" t="n">
+      <c r="E102" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F102" s="1" t="n">
+      <c r="F102" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="G102" s="2" t="n">
+      <c r="G102" s="3" t="n">
         <v>224102.58</v>
       </c>
-      <c r="H102" s="2" t="n">
+      <c r="H102" s="3" t="n">
         <v>139302.1626</v>
       </c>
-      <c r="I102" s="2" t="n">
+      <c r="I102" s="3" t="n">
         <v>84800.4174000001</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="B103" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C103" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D103" s="0" t="s">
+      <c r="C103" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E103" s="1" t="n">
+      <c r="E103" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F103" s="1" t="n">
+      <c r="F103" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="G103" s="2" t="n">
+      <c r="G103" s="3" t="n">
         <v>247943.280000001</v>
       </c>
-      <c r="H103" s="2" t="n">
+      <c r="H103" s="3" t="n">
         <v>154121.5416</v>
       </c>
-      <c r="I103" s="2" t="n">
+      <c r="I103" s="3" t="n">
         <v>93821.7384000002</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="B104" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C104" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D104" s="0" t="s">
+      <c r="C104" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E104" s="1" t="n">
+      <c r="E104" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F104" s="1" t="n">
+      <c r="F104" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="G104" s="2" t="n">
+      <c r="G104" s="3" t="n">
         <v>209798.16</v>
       </c>
-      <c r="H104" s="2" t="n">
+      <c r="H104" s="3" t="n">
         <v>130410.5352</v>
       </c>
-      <c r="I104" s="2" t="n">
+      <c r="I104" s="3" t="n">
         <v>79387.6248000001</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="A105" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="B105" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C105" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D105" s="0" t="s">
+      <c r="C105" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E105" s="1" t="n">
+      <c r="E105" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F105" s="1" t="n">
+      <c r="F105" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="G105" s="2" t="n">
+      <c r="G105" s="3" t="n">
         <v>121587.57</v>
       </c>
-      <c r="H105" s="2" t="n">
+      <c r="H105" s="3" t="n">
         <v>75578.8329</v>
       </c>
-      <c r="I105" s="2" t="n">
+      <c r="I105" s="3" t="n">
         <v>46008.7371</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
+      <c r="A106" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B106" s="0" t="s">
+      <c r="B106" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C106" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D106" s="0" t="s">
+      <c r="C106" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E106" s="1" t="n">
+      <c r="E106" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F106" s="1" t="n">
+      <c r="F106" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="G106" s="2" t="n">
+      <c r="G106" s="3" t="n">
         <v>135891.99</v>
       </c>
-      <c r="H106" s="2" t="n">
+      <c r="H106" s="3" t="n">
         <v>84470.4603</v>
       </c>
-      <c r="I106" s="2" t="n">
+      <c r="I106" s="3" t="n">
         <v>51421.5297</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
+      <c r="A107" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="B107" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C107" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D107" s="0" t="s">
+      <c r="C107" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E107" s="1" t="n">
+      <c r="E107" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F107" s="1" t="n">
+      <c r="F107" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="G107" s="2" t="n">
+      <c r="G107" s="3" t="n">
         <v>123971.64</v>
       </c>
-      <c r="H107" s="2" t="n">
+      <c r="H107" s="3" t="n">
         <v>77060.7708</v>
       </c>
-      <c r="I107" s="2" t="n">
+      <c r="I107" s="3" t="n">
         <v>46910.8692</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
+      <c r="A108" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B108" s="0" t="s">
+      <c r="B108" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C108" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D108" s="0" t="s">
+      <c r="C108" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E108" s="1" t="n">
+      <c r="E108" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F108" s="1" t="n">
+      <c r="F108" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="G108" s="2" t="n">
+      <c r="G108" s="3" t="n">
         <v>128739.78</v>
       </c>
-      <c r="H108" s="2" t="n">
+      <c r="H108" s="3" t="n">
         <v>80024.6466</v>
       </c>
-      <c r="I108" s="2" t="n">
+      <c r="I108" s="3" t="n">
         <v>48715.1334</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
+      <c r="A109" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B109" s="0" t="s">
+      <c r="B109" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C109" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D109" s="0" t="s">
+      <c r="C109" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E109" s="1" t="n">
+      <c r="E109" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F109" s="1" t="n">
+      <c r="F109" s="2" t="n">
         <v>111</v>
       </c>
-      <c r="G109" s="2" t="n">
+      <c r="G109" s="3" t="n">
         <v>264631.770000001</v>
       </c>
-      <c r="H109" s="2" t="n">
+      <c r="H109" s="3" t="n">
         <v>164495.1069</v>
       </c>
-      <c r="I109" s="2" t="n">
+      <c r="I109" s="3" t="n">
         <v>100136.6631</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="s">
+      <c r="A110" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B110" s="0" t="s">
+      <c r="B110" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C110" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D110" s="0" t="s">
+      <c r="C110" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E110" s="1" t="n">
+      <c r="E110" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F110" s="1" t="n">
+      <c r="F110" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="G110" s="2" t="n">
+      <c r="G110" s="3" t="n">
         <v>224102.58</v>
       </c>
-      <c r="H110" s="2" t="n">
+      <c r="H110" s="3" t="n">
         <v>139302.1626</v>
       </c>
-      <c r="I110" s="2" t="n">
+      <c r="I110" s="3" t="n">
         <v>84800.4174000001</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
+      <c r="A111" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="B111" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C111" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D111" s="0" t="s">
+      <c r="C111" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E111" s="1" t="n">
+      <c r="E111" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F111" s="1" t="n">
+      <c r="F111" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="G111" s="2" t="n">
+      <c r="G111" s="3" t="n">
         <v>236022.930000001</v>
       </c>
-      <c r="H111" s="2" t="n">
+      <c r="H111" s="3" t="n">
         <v>146711.8521</v>
       </c>
-      <c r="I111" s="2" t="n">
+      <c r="I111" s="3" t="n">
         <v>89311.0779000002</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
+      <c r="A112" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B112" s="0" t="s">
+      <c r="B112" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C112" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D112" s="0" t="s">
+      <c r="C112" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E112" s="1" t="n">
+      <c r="E112" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F112" s="1" t="n">
+      <c r="F112" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="G112" s="2" t="n">
+      <c r="G112" s="3" t="n">
         <v>207414.09</v>
       </c>
-      <c r="H112" s="2" t="n">
+      <c r="H112" s="3" t="n">
         <v>128928.5973</v>
       </c>
-      <c r="I112" s="2" t="n">
+      <c r="I112" s="3" t="n">
         <v>78485.4927000001</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
+      <c r="A113" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B113" s="0" t="s">
+      <c r="B113" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C113" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D113" s="0" t="s">
+      <c r="C113" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E113" s="1" t="n">
+      <c r="E113" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F113" s="1" t="n">
+      <c r="F113" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="G113" s="2" t="n">
+      <c r="G113" s="3" t="n">
         <v>49808.85</v>
       </c>
-      <c r="H113" s="2" t="n">
+      <c r="H113" s="3" t="n">
         <v>30961.1828</v>
       </c>
-      <c r="I113" s="2" t="n">
+      <c r="I113" s="3" t="n">
         <v>18847.6672</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
+      <c r="A114" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B114" s="0" t="s">
+      <c r="B114" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C114" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D114" s="0" t="s">
+      <c r="C114" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E114" s="1" t="n">
+      <c r="E114" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F114" s="1" t="n">
+      <c r="F114" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="G114" s="2" t="n">
+      <c r="G114" s="3" t="n">
         <v>57097.95</v>
       </c>
-      <c r="H114" s="2" t="n">
+      <c r="H114" s="3" t="n">
         <v>35492.0876</v>
       </c>
-      <c r="I114" s="2" t="n">
+      <c r="I114" s="3" t="n">
         <v>21605.8624</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
+      <c r="A115" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B115" s="0" t="s">
+      <c r="B115" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C115" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D115" s="0" t="s">
+      <c r="C115" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E115" s="1" t="n">
+      <c r="E115" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F115" s="1" t="n">
+      <c r="F115" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="G115" s="2" t="n">
+      <c r="G115" s="3" t="n">
         <v>41304.9</v>
       </c>
-      <c r="H115" s="2" t="n">
+      <c r="H115" s="3" t="n">
         <v>25675.1272</v>
       </c>
-      <c r="I115" s="2" t="n">
+      <c r="I115" s="3" t="n">
         <v>15629.7728</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
+      <c r="A116" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="B116" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C116" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D116" s="0" t="s">
+      <c r="C116" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E116" s="1" t="n">
+      <c r="E116" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F116" s="1" t="n">
+      <c r="F116" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="G116" s="2" t="n">
+      <c r="G116" s="3" t="n">
         <v>44949.45</v>
       </c>
-      <c r="H116" s="2" t="n">
+      <c r="H116" s="3" t="n">
         <v>27940.5796</v>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="I116" s="3" t="n">
         <v>17008.8704</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
+      <c r="A117" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="B117" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C117" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D117" s="0" t="s">
+      <c r="C117" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E117" s="1" t="n">
+      <c r="E117" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F117" s="1" t="n">
+      <c r="F117" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="G117" s="2" t="n">
+      <c r="G117" s="3" t="n">
         <v>59527.65</v>
       </c>
-      <c r="H117" s="2" t="n">
+      <c r="H117" s="3" t="n">
         <v>37002.3892</v>
       </c>
-      <c r="I117" s="2" t="n">
+      <c r="I117" s="3" t="n">
         <v>22525.2608</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
+      <c r="A118" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B118" s="0" t="s">
+      <c r="B118" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C118" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D118" s="0" t="s">
+      <c r="C118" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E118" s="1" t="n">
+      <c r="E118" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F118" s="1" t="n">
+      <c r="F118" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="G118" s="2" t="n">
+      <c r="G118" s="3" t="n">
         <v>59527.65</v>
       </c>
-      <c r="H118" s="2" t="n">
+      <c r="H118" s="3" t="n">
         <v>37002.3892</v>
       </c>
-      <c r="I118" s="2" t="n">
+      <c r="I118" s="3" t="n">
         <v>22525.2608</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
+      <c r="A119" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="B119" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C119" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D119" s="0" t="s">
+      <c r="C119" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E119" s="1" t="n">
+      <c r="E119" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F119" s="1" t="n">
+      <c r="F119" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G119" s="2" t="n">
+      <c r="G119" s="3" t="n">
         <v>54668.25</v>
       </c>
-      <c r="H119" s="2" t="n">
+      <c r="H119" s="3" t="n">
         <v>33981.786</v>
       </c>
-      <c r="I119" s="2" t="n">
+      <c r="I119" s="3" t="n">
         <v>20686.464</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
+      <c r="A120" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B120" s="0" t="s">
+      <c r="B120" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C120" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D120" s="0" t="s">
+      <c r="C120" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E120" s="1" t="n">
+      <c r="E120" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F120" s="1" t="n">
+      <c r="F120" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="G120" s="2" t="n">
+      <c r="G120" s="3" t="n">
         <v>71676.15</v>
       </c>
-      <c r="H120" s="2" t="n">
+      <c r="H120" s="3" t="n">
         <v>44553.8972</v>
       </c>
-      <c r="I120" s="2" t="n">
+      <c r="I120" s="3" t="n">
         <v>27122.2528</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
+      <c r="A121" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="B121" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C121" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D121" s="0" t="s">
+      <c r="C121" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E121" s="1" t="n">
+      <c r="E121" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F121" s="1" t="n">
+      <c r="F121" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="G121" s="2" t="n">
+      <c r="G121" s="3" t="n">
         <v>14104.65</v>
       </c>
-      <c r="H121" s="2" t="n">
+      <c r="H121" s="3" t="n">
         <v>8767.4512</v>
       </c>
-      <c r="I121" s="2" t="n">
+      <c r="I121" s="3" t="n">
         <v>5337.1988</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
+      <c r="A122" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B122" s="0" t="s">
+      <c r="B122" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C122" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D122" s="0" t="s">
+      <c r="C122" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E122" s="1" t="n">
+      <c r="E122" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F122" s="1" t="n">
+      <c r="F122" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="G122" s="2" t="n">
+      <c r="G122" s="3" t="n">
         <v>15589.35</v>
       </c>
-      <c r="H122" s="2" t="n">
+      <c r="H122" s="3" t="n">
         <v>9690.3408</v>
       </c>
-      <c r="I122" s="2" t="n">
+      <c r="I122" s="3" t="n">
         <v>5899.0092</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
+      <c r="A123" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B123" s="0" t="s">
+      <c r="B123" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C123" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D123" s="0" t="s">
+      <c r="C123" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E123" s="1" t="n">
+      <c r="E123" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F123" s="1" t="n">
+      <c r="F123" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="G123" s="2" t="n">
+      <c r="G123" s="3" t="n">
         <v>18558.75</v>
       </c>
-      <c r="H123" s="2" t="n">
+      <c r="H123" s="3" t="n">
         <v>11536.12</v>
       </c>
-      <c r="I123" s="2" t="n">
+      <c r="I123" s="3" t="n">
         <v>7022.63</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="s">
+      <c r="A124" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B124" s="0" t="s">
+      <c r="B124" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C124" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D124" s="0" t="s">
+      <c r="C124" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E124" s="1" t="n">
+      <c r="E124" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F124" s="1" t="n">
+      <c r="F124" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="G124" s="2" t="n">
+      <c r="G124" s="3" t="n">
         <v>19301.1</v>
       </c>
-      <c r="H124" s="2" t="n">
+      <c r="H124" s="3" t="n">
         <v>11997.5648</v>
       </c>
-      <c r="I124" s="2" t="n">
+      <c r="I124" s="3" t="n">
         <v>7303.5352</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
+      <c r="A125" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B125" s="0" t="s">
+      <c r="B125" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C125" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D125" s="0" t="s">
+      <c r="C125" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E125" s="1" t="n">
+      <c r="E125" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F125" s="1" t="n">
+      <c r="F125" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="G125" s="2" t="n">
+      <c r="G125" s="3" t="n">
         <v>16331.7</v>
       </c>
-      <c r="H125" s="2" t="n">
+      <c r="H125" s="3" t="n">
         <v>10151.7856</v>
       </c>
-      <c r="I125" s="2" t="n">
+      <c r="I125" s="3" t="n">
         <v>6179.9144</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="s">
+      <c r="A126" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="B126" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C126" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D126" s="0" t="s">
+      <c r="C126" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E126" s="1" t="n">
+      <c r="E126" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F126" s="1" t="n">
+      <c r="F126" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="G126" s="2" t="n">
+      <c r="G126" s="3" t="n">
         <v>31178.7</v>
       </c>
-      <c r="H126" s="2" t="n">
+      <c r="H126" s="3" t="n">
         <v>19380.6816</v>
       </c>
-      <c r="I126" s="2" t="n">
+      <c r="I126" s="3" t="n">
         <v>11798.0184</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="s">
+      <c r="A127" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="B127" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C127" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D127" s="0" t="s">
+      <c r="C127" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E127" s="1" t="n">
+      <c r="E127" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F127" s="1" t="n">
+      <c r="F127" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="G127" s="2" t="n">
+      <c r="G127" s="3" t="n">
         <v>23755.2</v>
       </c>
-      <c r="H127" s="2" t="n">
+      <c r="H127" s="3" t="n">
         <v>14766.2336</v>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I127" s="3" t="n">
         <v>8988.9664</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="s">
+      <c r="A128" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="B128" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C128" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D128" s="0" t="s">
+      <c r="C128" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E128" s="1" t="n">
+      <c r="E128" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F128" s="1" t="n">
+      <c r="F128" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G128" s="2" t="n">
+      <c r="G128" s="3" t="n">
         <v>25982.25</v>
       </c>
-      <c r="H128" s="2" t="n">
+      <c r="H128" s="3" t="n">
         <v>16150.568</v>
       </c>
-      <c r="I128" s="2" t="n">
+      <c r="I128" s="3" t="n">
         <v>9831.682</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
+      <c r="A129" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B129" s="0" t="s">
+      <c r="B129" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C129" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D129" s="0" t="s">
+      <c r="C129" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E129" s="1" t="n">
+      <c r="E129" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F129" s="1" t="n">
+      <c r="F129" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="G129" s="2" t="n">
+      <c r="G129" s="3" t="n">
         <v>16331.7</v>
       </c>
-      <c r="H129" s="2" t="n">
+      <c r="H129" s="3" t="n">
         <v>10151.7856</v>
       </c>
-      <c r="I129" s="2" t="n">
+      <c r="I129" s="3" t="n">
         <v>6179.9144</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="s">
+      <c r="A130" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B130" s="0" t="s">
+      <c r="B130" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C130" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D130" s="0" t="s">
+      <c r="C130" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E130" s="1" t="n">
+      <c r="E130" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F130" s="1" t="n">
+      <c r="F130" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G130" s="2" t="n">
+      <c r="G130" s="3" t="n">
         <v>22270.5</v>
       </c>
-      <c r="H130" s="2" t="n">
+      <c r="H130" s="3" t="n">
         <v>13843.344</v>
       </c>
-      <c r="I130" s="2" t="n">
+      <c r="I130" s="3" t="n">
         <v>8427.156</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
+      <c r="A131" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B131" s="0" t="s">
+      <c r="B131" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C131" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D131" s="0" t="s">
+      <c r="C131" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E131" s="1" t="n">
+      <c r="E131" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F131" s="1" t="n">
+      <c r="F131" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="G131" s="2" t="n">
+      <c r="G131" s="3" t="n">
         <v>16331.7</v>
       </c>
-      <c r="H131" s="2" t="n">
+      <c r="H131" s="3" t="n">
         <v>10151.7856</v>
       </c>
-      <c r="I131" s="2" t="n">
+      <c r="I131" s="3" t="n">
         <v>6179.9144</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="s">
+      <c r="A132" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B132" s="0" t="s">
+      <c r="B132" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C132" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D132" s="0" t="s">
+      <c r="C132" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E132" s="1" t="n">
+      <c r="E132" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F132" s="1" t="n">
+      <c r="F132" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="G132" s="2" t="n">
+      <c r="G132" s="3" t="n">
         <v>17074.05</v>
       </c>
-      <c r="H132" s="2" t="n">
+      <c r="H132" s="3" t="n">
         <v>10613.2304</v>
       </c>
-      <c r="I132" s="2" t="n">
+      <c r="I132" s="3" t="n">
         <v>6460.8196</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0" t="s">
+      <c r="A133" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B133" s="0" t="s">
+      <c r="B133" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C133" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D133" s="0" t="s">
+      <c r="C133" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E133" s="1" t="n">
+      <c r="E133" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F133" s="1" t="n">
+      <c r="F133" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="G133" s="2" t="n">
+      <c r="G133" s="3" t="n">
         <v>16331.7</v>
       </c>
-      <c r="H133" s="2" t="n">
+      <c r="H133" s="3" t="n">
         <v>10151.7856</v>
       </c>
-      <c r="I133" s="2" t="n">
+      <c r="I133" s="3" t="n">
         <v>6179.9144</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="0" t="s">
+      <c r="A134" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B134" s="0" t="s">
+      <c r="B134" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C134" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D134" s="0" t="s">
+      <c r="C134" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E134" s="1" t="n">
+      <c r="E134" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F134" s="1" t="n">
+      <c r="F134" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="G134" s="2" t="n">
+      <c r="G134" s="3" t="n">
         <v>13362.3</v>
       </c>
-      <c r="H134" s="2" t="n">
+      <c r="H134" s="3" t="n">
         <v>8306.0064</v>
       </c>
-      <c r="I134" s="2" t="n">
+      <c r="I134" s="3" t="n">
         <v>5056.2936</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0" t="s">
+      <c r="A135" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B135" s="0" t="s">
+      <c r="B135" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C135" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D135" s="0" t="s">
+      <c r="C135" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E135" s="1" t="n">
+      <c r="E135" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F135" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G135" s="2" t="n">
+      <c r="F135" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G135" s="3" t="n">
         <v>11877.6</v>
       </c>
-      <c r="H135" s="2" t="n">
+      <c r="H135" s="3" t="n">
         <v>7383.1168</v>
       </c>
-      <c r="I135" s="2" t="n">
+      <c r="I135" s="3" t="n">
         <v>4494.4832</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="0" t="s">
+      <c r="A136" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B136" s="0" t="s">
+      <c r="B136" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C136" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D136" s="0" t="s">
+      <c r="C136" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E136" s="1" t="n">
+      <c r="E136" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F136" s="1" t="n">
+      <c r="F136" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G136" s="2" t="n">
+      <c r="G136" s="3" t="n">
         <v>22270.5</v>
       </c>
-      <c r="H136" s="2" t="n">
+      <c r="H136" s="3" t="n">
         <v>13843.344</v>
       </c>
-      <c r="I136" s="2" t="n">
+      <c r="I136" s="3" t="n">
         <v>8427.156</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="0" t="s">
+      <c r="A137" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B137" s="0" t="s">
+      <c r="B137" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C137" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D137" s="0" t="s">
+      <c r="C137" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E137" s="1" t="n">
+      <c r="E137" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F137" s="1" t="n">
+      <c r="F137" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="G137" s="2" t="n">
+      <c r="G137" s="3" t="n">
         <v>24497.55</v>
       </c>
-      <c r="H137" s="2" t="n">
+      <c r="H137" s="3" t="n">
         <v>15227.6784</v>
       </c>
-      <c r="I137" s="2" t="n">
+      <c r="I137" s="3" t="n">
         <v>9269.8716</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="0" t="s">
+      <c r="A138" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B138" s="0" t="s">
+      <c r="B138" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C138" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D138" s="0" t="s">
+      <c r="C138" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E138" s="1" t="n">
+      <c r="E138" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F138" s="1" t="n">
+      <c r="F138" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="G138" s="2" t="n">
+      <c r="G138" s="3" t="n">
         <v>27466.95</v>
       </c>
-      <c r="H138" s="2" t="n">
+      <c r="H138" s="3" t="n">
         <v>17073.4576</v>
       </c>
-      <c r="I138" s="2" t="n">
+      <c r="I138" s="3" t="n">
         <v>10393.4924</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="0" t="s">
+      <c r="A139" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B139" s="0" t="s">
+      <c r="B139" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C139" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D139" s="0" t="s">
+      <c r="C139" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E139" s="1" t="n">
+      <c r="E139" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F139" s="1" t="n">
+      <c r="F139" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G139" s="2" t="n">
+      <c r="G139" s="3" t="n">
         <v>22270.5</v>
       </c>
-      <c r="H139" s="2" t="n">
+      <c r="H139" s="3" t="n">
         <v>13843.344</v>
       </c>
-      <c r="I139" s="2" t="n">
+      <c r="I139" s="3" t="n">
         <v>8427.156</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="0" t="s">
+      <c r="A140" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B140" s="0" t="s">
+      <c r="B140" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C140" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="D140" s="0" t="s">
+      <c r="C140" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E140" s="1" t="n">
+      <c r="E140" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="F140" s="1" t="n">
+      <c r="F140" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="G140" s="2" t="n">
+      <c r="G140" s="3" t="n">
         <v>18558.75</v>
       </c>
-      <c r="H140" s="2" t="n">
+      <c r="H140" s="3" t="n">
         <v>11536.12</v>
       </c>
-      <c r="I140" s="2" t="n">
+      <c r="I140" s="3" t="n">
         <v>7022.63</v>
       </c>
     </row>
@@ -7223,444 +7209,444 @@
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="11.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="10.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="11.03"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="11" t="n">
         <v>2021</v>
       </c>
-      <c r="D2" s="11" t="n">
+      <c r="D2" s="12" t="n">
         <v>2022</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>11745.012</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="18" t="n">
         <v>11545.944</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <v>23290.956</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="20" t="n">
         <f aca="false">D3-C3</f>
-        <v>-199.067999999999</v>
+        <v>-199.068000000001</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="21" t="n">
         <v>10141.2</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="21" t="n">
         <v>12545.04</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>22686.24</v>
       </c>
-      <c r="F4" s="21" t="n">
+      <c r="F4" s="22" t="n">
         <f aca="false">D4-C4</f>
-        <v>2403.84000000003</v>
+        <v>2403.84</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="24" t="n">
-        <v>798965.105400004</v>
-      </c>
-      <c r="D5" s="25" t="n">
-        <v>682940.656800002</v>
-      </c>
-      <c r="E5" s="26" t="n">
+      <c r="C5" s="25" t="n">
+        <v>798965.105400003</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>682940.656800003</v>
+      </c>
+      <c r="E5" s="27" t="n">
         <v>1481905.76220001</v>
       </c>
-      <c r="F5" s="21" t="n">
+      <c r="F5" s="22" t="n">
         <f aca="false">D5-C5</f>
-        <v>-116024.448600001</v>
+        <v>-116024.4486</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27"/>
-      <c r="B6" s="28" t="s">
+      <c r="A6" s="28"/>
+      <c r="B6" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="29" t="n">
-        <v>771433.033299999</v>
-      </c>
-      <c r="D6" s="30" t="n">
-        <v>683705.172899999</v>
-      </c>
-      <c r="E6" s="31" t="n">
+      <c r="C6" s="30" t="n">
+        <v>771433.0333</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>683705.1729</v>
+      </c>
+      <c r="E6" s="32" t="n">
         <v>1455138.2062</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="22" t="n">
         <f aca="false">D6-C6</f>
-        <v>-87727.8603999999</v>
+        <v>-87727.8604000001</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="21" t="n">
         <v>70991.4548</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="21" t="n">
         <v>115404.828</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>186396.2828</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="22" t="n">
         <f aca="false">D7-C7</f>
-        <v>44413.3731999998</v>
+        <v>44413.3732</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="25" t="n">
         <v>24295.6197</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="26" t="n">
         <v>36566.1347</v>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="27" t="n">
         <v>60861.7544</v>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F8" s="22" t="n">
         <f aca="false">D8-C8</f>
         <v>12270.515</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27"/>
-      <c r="B9" s="28" t="s">
+      <c r="A9" s="28"/>
+      <c r="B9" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>23879.8053</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="31" t="n">
         <v>33893.9172</v>
       </c>
-      <c r="E9" s="31" t="n">
+      <c r="E9" s="32" t="n">
         <v>57773.7225</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="22" t="n">
         <f aca="false">D9-C9</f>
         <v>10014.1119</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="32" t="n">
-        <v>492422.616400001</v>
-      </c>
-      <c r="D10" s="32" t="n">
+      <c r="C10" s="33" t="n">
+        <v>492422.6164</v>
+      </c>
+      <c r="D10" s="33" t="n">
         <v>201445.6158</v>
       </c>
-      <c r="E10" s="26" t="n">
-        <v>693868.232200001</v>
-      </c>
-      <c r="F10" s="21" t="n">
+      <c r="E10" s="27" t="n">
+        <v>693868.2322</v>
+      </c>
+      <c r="F10" s="22" t="n">
         <f aca="false">D10-C10</f>
         <v>-290977.0006</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28" t="s">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="34" t="n">
         <v>290100.2662</v>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="34" t="n">
         <v>54235.3581</v>
       </c>
-      <c r="E11" s="31" t="n">
+      <c r="E11" s="32" t="n">
         <v>344335.6243</v>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="F11" s="22" t="n">
         <f aca="false">D11-C11</f>
         <v>-235864.9081</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>192347.28</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>371088</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>563435.28</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="22" t="n">
         <f aca="false">D12-C12</f>
         <v>178740.72</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="21" t="n">
         <v>242005.2279</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="21" t="n">
         <v>237267.7683</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>479272.9962</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="22" t="n">
         <f aca="false">D13-C13</f>
-        <v>-4737.45960000003</v>
+        <v>-4737.45959999997</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="25" t="n">
         <v>46610.1597</v>
       </c>
-      <c r="D14" s="34"/>
-      <c r="E14" s="26" t="n">
+      <c r="D14" s="35"/>
+      <c r="E14" s="27" t="n">
         <v>46610.1597</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="22" t="n">
         <f aca="false">D14-C14</f>
         <v>-46610.1597</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27"/>
-      <c r="B15" s="28" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="30" t="n">
         <v>48611.823</v>
       </c>
-      <c r="D15" s="35"/>
-      <c r="E15" s="31" t="n">
+      <c r="D15" s="36"/>
+      <c r="E15" s="32" t="n">
         <v>48611.823</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="22" t="n">
         <f aca="false">D15-C15</f>
         <v>-48611.823</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="21" t="n">
         <v>117018.8784</v>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" s="21" t="n">
         <v>162177.1704</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="19" t="n">
         <v>279196.0488</v>
       </c>
-      <c r="F16" s="21" t="n">
+      <c r="F16" s="22" t="n">
         <f aca="false">D16-C16</f>
-        <v>45158.2920000002</v>
+        <v>45158.2920000004</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="C17" s="25" t="n">
         <v>202077.5904</v>
       </c>
-      <c r="D17" s="25" t="n">
-        <v>364461.368400001</v>
-      </c>
-      <c r="E17" s="26" t="n">
+      <c r="D17" s="26" t="n">
+        <v>364461.3684</v>
+      </c>
+      <c r="E17" s="27" t="n">
         <v>566538.958800001</v>
       </c>
-      <c r="F17" s="21" t="n">
+      <c r="F17" s="22" t="n">
         <f aca="false">D17-C17</f>
         <v>162383.778</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27"/>
-      <c r="B18" s="28" t="s">
+      <c r="A18" s="28"/>
+      <c r="B18" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="30" t="n">
         <v>193056.2694</v>
       </c>
-      <c r="D18" s="30" t="n">
-        <v>352733.651100001</v>
-      </c>
-      <c r="E18" s="31" t="n">
-        <v>545789.920500001</v>
-      </c>
-      <c r="F18" s="21" t="n">
+      <c r="D18" s="31" t="n">
+        <v>352733.6511</v>
+      </c>
+      <c r="E18" s="32" t="n">
+        <v>545789.9205</v>
+      </c>
+      <c r="F18" s="22" t="n">
         <f aca="false">D18-C18</f>
         <v>159677.3817</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="20" t="n">
-        <v>73092.1727999999</v>
-      </c>
-      <c r="D19" s="20" t="n">
-        <v>92859.2383999999</v>
-      </c>
-      <c r="E19" s="18" t="n">
+      <c r="C19" s="21" t="n">
+        <v>73092.1728</v>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>92859.2384</v>
+      </c>
+      <c r="E19" s="19" t="n">
         <v>165951.4112</v>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="F19" s="22" t="n">
         <f aca="false">D19-C19</f>
         <v>19767.0656</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="24" t="n">
+      <c r="C20" s="25" t="n">
         <v>31742.2876</v>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D20" s="26" t="n">
         <v>45225.7372</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="27" t="n">
         <v>76968.0248</v>
       </c>
-      <c r="F20" s="21" t="n">
+      <c r="F20" s="22" t="n">
         <f aca="false">D20-C20</f>
         <v>13483.4496</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28" t="s">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="30" t="n">
         <v>28371.4252</v>
       </c>
-      <c r="D21" s="30" t="n">
+      <c r="D21" s="31" t="n">
         <v>43540.306</v>
       </c>
-      <c r="E21" s="31" t="n">
+      <c r="E21" s="32" t="n">
         <v>71911.7312</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F21" s="22" t="n">
         <f aca="false">D21-C21</f>
         <v>15168.8808</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="38" t="n">
+      <c r="B22" s="38"/>
+      <c r="C22" s="39" t="n">
         <v>3668907.2275</v>
       </c>
-      <c r="D22" s="39" t="n">
+      <c r="D22" s="40" t="n">
         <v>3501635.9073</v>
       </c>
-      <c r="E22" s="40" t="n">
+      <c r="E22" s="41" t="n">
         <v>7170543.13480001</v>
       </c>
-      <c r="F22" s="41" t="n">
+      <c r="F22" s="42" t="n">
         <f aca="false">D22-C22</f>
-        <v>-167271.320200002</v>
+        <v>-167271.3202</v>
       </c>
     </row>
   </sheetData>
@@ -7679,461 +7665,542 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.03"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="42" t="n">
+      <c r="C1" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="44" t="n">
         <v>2021</v>
       </c>
-      <c r="D1" s="42" t="n">
+      <c r="E1" s="44" t="n">
         <v>2022</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="F1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="45" t="n">
+      <c r="C2" s="46" t="str">
+        <f aca="false">LEFT(A2,SEARCH("-",A2)-1)&amp;" "&amp;B2</f>
+        <v>Road Black</v>
+      </c>
+      <c r="D2" s="47" t="n">
         <v>492422.616400001</v>
       </c>
-      <c r="D2" s="45" t="n">
+      <c r="E2" s="47" t="n">
         <v>201445.6158</v>
       </c>
-      <c r="E2" s="46" t="n">
+      <c r="F2" s="48" t="n">
         <v>693868.232200001</v>
       </c>
-      <c r="F2" s="21" t="n">
-        <f aca="false">D2-C2</f>
-        <v>-290977.0006</v>
+      <c r="G2" s="22" t="n">
+        <f aca="false">E2-D2</f>
+        <v>-290977.000600001</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="45" t="n">
+      <c r="C3" s="46" t="str">
+        <f aca="false">LEFT(A3,SEARCH("-",A3)-1)&amp;" "&amp;B3</f>
+        <v>Road Red</v>
+      </c>
+      <c r="D3" s="47" t="n">
         <v>290100.2662</v>
       </c>
-      <c r="D3" s="45" t="n">
+      <c r="E3" s="47" t="n">
         <v>54235.3581</v>
       </c>
-      <c r="E3" s="46" t="n">
+      <c r="F3" s="48" t="n">
         <v>344335.6243</v>
       </c>
-      <c r="F3" s="21" t="n">
-        <f aca="false">D3-C3</f>
+      <c r="G3" s="22" t="n">
+        <f aca="false">E3-D3</f>
         <v>-235864.9081</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="45" t="n">
+      <c r="C4" s="46" t="str">
+        <f aca="false">LEFT(A4,SEARCH("-",A4)-1)&amp;" "&amp;B4</f>
+        <v>Mountain Black</v>
+      </c>
+      <c r="D4" s="47" t="n">
         <v>798965.105400004</v>
       </c>
-      <c r="D4" s="45" t="n">
+      <c r="E4" s="47" t="n">
         <v>682940.656800002</v>
       </c>
-      <c r="E4" s="46" t="n">
+      <c r="F4" s="48" t="n">
         <v>1481905.76220001</v>
       </c>
-      <c r="F4" s="21" t="n">
-        <f aca="false">D4-C4</f>
-        <v>-116024.448600001</v>
+      <c r="G4" s="22" t="n">
+        <f aca="false">E4-D4</f>
+        <v>-116024.448600002</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="45" t="n">
+      <c r="C5" s="46" t="str">
+        <f aca="false">LEFT(A5,SEARCH("-",A5)-1)&amp;" "&amp;B5</f>
+        <v>Mountain Silver</v>
+      </c>
+      <c r="D5" s="47" t="n">
         <v>771433.033299999</v>
       </c>
-      <c r="D5" s="45" t="n">
+      <c r="E5" s="47" t="n">
         <v>683705.172899999</v>
       </c>
-      <c r="E5" s="46" t="n">
+      <c r="F5" s="48" t="n">
         <v>1455138.2062</v>
       </c>
-      <c r="F5" s="21" t="n">
-        <f aca="false">D5-C5</f>
-        <v>-87727.8603999999</v>
+      <c r="G5" s="22" t="n">
+        <f aca="false">E5-D5</f>
+        <v>-87727.8604</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="45" t="n">
+      <c r="C6" s="46" t="str">
+        <f aca="false">LEFT(A6,SEARCH("-",A6)-1)&amp;" "&amp;B6</f>
+        <v>Road Red</v>
+      </c>
+      <c r="D6" s="47" t="n">
         <v>48611.823</v>
       </c>
-      <c r="D6" s="47"/>
-      <c r="E6" s="46" t="n">
+      <c r="E6" s="49"/>
+      <c r="F6" s="48" t="n">
         <v>48611.823</v>
       </c>
-      <c r="F6" s="21" t="n">
-        <f aca="false">D6-C6</f>
+      <c r="G6" s="22" t="n">
+        <f aca="false">E6-D6</f>
         <v>-48611.823</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="45" t="n">
+      <c r="C7" s="46" t="str">
+        <f aca="false">LEFT(A7,SEARCH("-",A7)-1)&amp;" "&amp;B7</f>
+        <v>Road Black</v>
+      </c>
+      <c r="D7" s="47" t="n">
         <v>46610.1597</v>
       </c>
-      <c r="D7" s="47"/>
-      <c r="E7" s="46" t="n">
+      <c r="E7" s="49"/>
+      <c r="F7" s="48" t="n">
         <v>46610.1597</v>
       </c>
-      <c r="F7" s="21" t="n">
-        <f aca="false">D7-C7</f>
+      <c r="G7" s="22" t="n">
+        <f aca="false">E7-D7</f>
         <v>-46610.1597</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C8" s="46" t="str">
+        <f aca="false">LEFT(A8,SEARCH("-",A8)-1)&amp;" "&amp;B8</f>
+        <v>Road Yellow</v>
+      </c>
+      <c r="D8" s="47" t="n">
         <v>242005.2279</v>
       </c>
-      <c r="D8" s="45" t="n">
+      <c r="E8" s="47" t="n">
         <v>237267.7683</v>
       </c>
-      <c r="E8" s="46" t="n">
+      <c r="F8" s="48" t="n">
         <v>479272.9962</v>
       </c>
-      <c r="F8" s="21" t="n">
-        <f aca="false">D8-C8</f>
-        <v>-4737.45960000003</v>
+      <c r="G8" s="22" t="n">
+        <f aca="false">E8-D8</f>
+        <v>-4737.4596</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="45" t="n">
+      <c r="C9" s="46" t="str">
+        <f aca="false">LEFT(A9,SEARCH("-",A9)-1)&amp;" "&amp;B9</f>
+        <v>All NA</v>
+      </c>
+      <c r="D9" s="47" t="n">
         <v>11745.012</v>
       </c>
-      <c r="D9" s="45" t="n">
+      <c r="E9" s="47" t="n">
         <v>11545.944</v>
       </c>
-      <c r="E9" s="46" t="n">
+      <c r="F9" s="48" t="n">
         <v>23290.956</v>
       </c>
-      <c r="F9" s="21" t="n">
-        <f aca="false">D9-C9</f>
-        <v>-199.067999999999</v>
+      <c r="G9" s="22" t="n">
+        <f aca="false">E9-D9</f>
+        <v>-199.068000000001</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="45" t="n">
+      <c r="C10" s="46" t="str">
+        <f aca="false">LEFT(A10,SEARCH("-",A10)-1)&amp;" "&amp;B10</f>
+        <v>Hitch Rack  NA</v>
+      </c>
+      <c r="D10" s="47" t="n">
         <v>10141.2</v>
       </c>
-      <c r="D10" s="45" t="n">
+      <c r="E10" s="47" t="n">
         <v>12545.04</v>
       </c>
-      <c r="E10" s="46" t="n">
+      <c r="F10" s="48" t="n">
         <v>22686.24</v>
       </c>
-      <c r="F10" s="21" t="n">
-        <f aca="false">D10-C10</f>
-        <v>2403.84000000003</v>
+      <c r="G10" s="22" t="n">
+        <f aca="false">E10-D10</f>
+        <v>2403.84</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="45" t="n">
+      <c r="C11" s="46" t="str">
+        <f aca="false">LEFT(A11,SEARCH("-",A11)-1)&amp;" "&amp;B11</f>
+        <v>Mountain Silver</v>
+      </c>
+      <c r="D11" s="47" t="n">
         <v>23879.8053</v>
       </c>
-      <c r="D11" s="45" t="n">
+      <c r="E11" s="47" t="n">
         <v>33893.9172</v>
       </c>
-      <c r="E11" s="46" t="n">
+      <c r="F11" s="48" t="n">
         <v>57773.7225</v>
       </c>
-      <c r="F11" s="21" t="n">
-        <f aca="false">D11-C11</f>
+      <c r="G11" s="22" t="n">
+        <f aca="false">E11-D11</f>
         <v>10014.1119</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="45" t="n">
+      <c r="C12" s="46" t="str">
+        <f aca="false">LEFT(A12,SEARCH("-",A12)-1)&amp;" "&amp;B12</f>
+        <v>Mountain Black</v>
+      </c>
+      <c r="D12" s="47" t="n">
         <v>24295.6197</v>
       </c>
-      <c r="D12" s="45" t="n">
+      <c r="E12" s="47" t="n">
         <v>36566.1347</v>
       </c>
-      <c r="E12" s="46" t="n">
+      <c r="F12" s="48" t="n">
         <v>60861.7544</v>
       </c>
-      <c r="F12" s="21" t="n">
-        <f aca="false">D12-C12</f>
+      <c r="G12" s="22" t="n">
+        <f aca="false">E12-D12</f>
         <v>12270.515</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="45" t="n">
+      <c r="C13" s="46" t="str">
+        <f aca="false">LEFT(A13,SEARCH("-",A13)-1)&amp;" "&amp;B13</f>
+        <v>Touring Blue</v>
+      </c>
+      <c r="D13" s="47" t="n">
         <v>31742.2876</v>
       </c>
-      <c r="D13" s="45" t="n">
+      <c r="E13" s="47" t="n">
         <v>45225.7372</v>
       </c>
-      <c r="E13" s="46" t="n">
+      <c r="F13" s="48" t="n">
         <v>76968.0248</v>
       </c>
-      <c r="F13" s="21" t="n">
-        <f aca="false">D13-C13</f>
+      <c r="G13" s="22" t="n">
+        <f aca="false">E13-D13</f>
         <v>13483.4496</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="45" t="n">
+      <c r="C14" s="46" t="str">
+        <f aca="false">LEFT(A14,SEARCH("-",A14)-1)&amp;" "&amp;B14</f>
+        <v>Touring Yellow</v>
+      </c>
+      <c r="D14" s="47" t="n">
         <v>28371.4252</v>
       </c>
-      <c r="D14" s="45" t="n">
+      <c r="E14" s="47" t="n">
         <v>43540.306</v>
       </c>
-      <c r="E14" s="46" t="n">
+      <c r="F14" s="48" t="n">
         <v>71911.7312</v>
       </c>
-      <c r="F14" s="21" t="n">
-        <f aca="false">D14-C14</f>
+      <c r="G14" s="22" t="n">
+        <f aca="false">E14-D14</f>
         <v>15168.8808</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="45" t="n">
+      <c r="C15" s="46" t="str">
+        <f aca="false">LEFT(A15,SEARCH("-",A15)-1)&amp;" "&amp;B15</f>
+        <v>Touring Blue</v>
+      </c>
+      <c r="D15" s="47" t="n">
         <v>73092.1727999999</v>
       </c>
-      <c r="D15" s="45" t="n">
+      <c r="E15" s="47" t="n">
         <v>92859.2383999999</v>
       </c>
-      <c r="E15" s="46" t="n">
+      <c r="F15" s="48" t="n">
         <v>165951.4112</v>
       </c>
-      <c r="F15" s="21" t="n">
-        <f aca="false">D15-C15</f>
+      <c r="G15" s="22" t="n">
+        <f aca="false">E15-D15</f>
         <v>19767.0656</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="45" t="n">
+      <c r="C16" s="46" t="str">
+        <f aca="false">LEFT(A16,SEARCH("-",A16)-1)&amp;" "&amp;B16</f>
+        <v>Mountain Silver</v>
+      </c>
+      <c r="D16" s="47" t="n">
         <v>70991.4548</v>
       </c>
-      <c r="D16" s="45" t="n">
+      <c r="E16" s="47" t="n">
         <v>115404.828</v>
       </c>
-      <c r="E16" s="46" t="n">
+      <c r="F16" s="48" t="n">
         <v>186396.2828</v>
       </c>
-      <c r="F16" s="21" t="n">
-        <f aca="false">D16-C16</f>
-        <v>44413.3731999998</v>
+      <c r="G16" s="22" t="n">
+        <f aca="false">E16-D16</f>
+        <v>44413.3732</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="45" t="n">
+      <c r="C17" s="46" t="str">
+        <f aca="false">LEFT(A17,SEARCH("-",A17)-1)&amp;" "&amp;B17</f>
+        <v>Road Black</v>
+      </c>
+      <c r="D17" s="47" t="n">
         <v>117018.8784</v>
       </c>
-      <c r="D17" s="45" t="n">
+      <c r="E17" s="47" t="n">
         <v>162177.1704</v>
       </c>
-      <c r="E17" s="46" t="n">
+      <c r="F17" s="48" t="n">
         <v>279196.0488</v>
       </c>
-      <c r="F17" s="21" t="n">
-        <f aca="false">D17-C17</f>
-        <v>45158.2920000002</v>
+      <c r="G17" s="22" t="n">
+        <f aca="false">E17-D17</f>
+        <v>45158.292</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="45" t="n">
+      <c r="C18" s="46" t="str">
+        <f aca="false">LEFT(A18,SEARCH("-",A18)-1)&amp;" "&amp;B18</f>
+        <v>Touring Yellow</v>
+      </c>
+      <c r="D18" s="47" t="n">
         <v>193056.2694</v>
       </c>
-      <c r="D18" s="45" t="n">
+      <c r="E18" s="47" t="n">
         <v>352733.651100001</v>
       </c>
-      <c r="E18" s="46" t="n">
+      <c r="F18" s="48" t="n">
         <v>545789.920500001</v>
       </c>
-      <c r="F18" s="21" t="n">
-        <f aca="false">D18-C18</f>
-        <v>159677.3817</v>
+      <c r="G18" s="22" t="n">
+        <f aca="false">E18-D18</f>
+        <v>159677.381700001</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="45" t="n">
+      <c r="C19" s="46" t="str">
+        <f aca="false">LEFT(A19,SEARCH("-",A19)-1)&amp;" "&amp;B19</f>
+        <v>Touring Blue</v>
+      </c>
+      <c r="D19" s="47" t="n">
         <v>202077.5904</v>
       </c>
-      <c r="D19" s="45" t="n">
+      <c r="E19" s="47" t="n">
         <v>364461.368400001</v>
       </c>
-      <c r="E19" s="46" t="n">
+      <c r="F19" s="48" t="n">
         <v>566538.958800001</v>
       </c>
-      <c r="F19" s="21" t="n">
-        <f aca="false">D19-C19</f>
-        <v>162383.778</v>
+      <c r="G19" s="22" t="n">
+        <f aca="false">E19-D19</f>
+        <v>162383.778000001</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="45" t="n">
+      <c r="C20" s="46" t="str">
+        <f aca="false">LEFT(A20,SEARCH("-",A20)-1)&amp;" "&amp;B20</f>
+        <v>Road Yellow</v>
+      </c>
+      <c r="D20" s="47" t="n">
         <v>192347.28</v>
       </c>
-      <c r="D20" s="45" t="n">
+      <c r="E20" s="47" t="n">
         <v>371088</v>
       </c>
-      <c r="E20" s="46" t="n">
+      <c r="F20" s="48" t="n">
         <v>563435.28</v>
       </c>
-      <c r="F20" s="21" t="n">
-        <f aca="false">D20-C20</f>
+      <c r="G20" s="22" t="n">
+        <f aca="false">E20-D20</f>
         <v>178740.72</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="48" t="s">
+      <c r="A21" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="50" t="n">
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="52" t="n">
         <v>3668907.2275</v>
       </c>
-      <c r="D21" s="50" t="n">
+      <c r="E21" s="52" t="n">
         <v>3501635.9073</v>
       </c>
-      <c r="E21" s="50" t="n">
+      <c r="F21" s="52" t="n">
         <v>7170543.13480001</v>
       </c>
-      <c r="F21" s="13" t="n">
-        <f aca="false">D21-C21</f>
-        <v>-167271.320200002</v>
+      <c r="G21" s="14" t="n">
+        <f aca="false">E21-D21</f>
+        <v>-167271.3202</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F1:F20">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+  <conditionalFormatting sqref="G1:G20">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>-50000</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>-50000</formula>
       <formula>-10000</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="4" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>-10000</formula>
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
